--- a/school_counselor_forms/010_student_adaptation_to_college_questionnaire--school_counselor_forms.xlsx
+++ b/school_counselor_forms/010_student_adaptation_to_college_questionnaire--school_counselor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>student_adaptation_to_college_questionnaire</t>
+          <t>adaptation_to_college</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>adaptation_to_college</t>
+          <t>How does the student adapt to college?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>student_background</t>
+          <t>What is the student's background?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>parental_involvement</t>
+          <t>How involved are the parents?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>student_involvement</t>
+          <t>How involved is the student?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>school_counselor_form</t>
+          <t>School Counselor Form</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>Is there anything else you'd like to share about the student?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Additional Notes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>student_adaptation_to_college_questionnaire</t>
+          <t>student_adaptation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>student_adaptation_to_college_questionnaire</t>
+          <t>Does the student adapt to college?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>student_adaptation_to_college_questionnaire</t>
+          <t>student_adaptation_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>student_adaptation_to_college_questionnaire</t>
+          <t>Student Adaptation 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,13 +732,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>What is the student's start date?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>What is the student's start time?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>school_name</t>
+          <t>School Name</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>school_year</t>
+          <t>School Year?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>student_grade</t>
+          <t>grade_level</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>student_grade</t>
+          <t>Student Grade Level?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>student_gender</t>
+          <t>Student Gender?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>student_ethnicity</t>
+          <t>Student Ethnicity?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>student_disability</t>
+          <t>Student Disability?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>School Phone?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>School Email?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>student_adaptation_to_college_questionnaire</t>
+          <t>student_adaptation_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>student_adaptation_to_college_questionnaire</t>
+          <t>Student Adaptation 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>student_adaptation_to_college_questionnaire</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>student_adaptation_to_college_questionnaire</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>school_email</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>School Email? (2)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,62 +1026,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>school_email</t>
+          <t>school_phone</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>school_email</t>
+          <t>School Phone? (2)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>school_phone</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>school_phone</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>student_adaptation_to_college_questionnaire</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>student_adaptation_to_college_questionnaire</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +1052,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,7 +1080,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>student_adaptation_to_college_questionnaire_choices</t>
+          <t>student_adaptation_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1097,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>student_adaptation_to_college_questionnaire_choices</t>
+          <t>student_adaptation_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +1114,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>student_adaptation_to_college_questionnaire_choices</t>
+          <t>student_adaptation_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1131,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>student_adaptation_to_college_questionnaire_choices</t>
+          <t>student_adaptation_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1199,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1170,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1250,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>student_adaptation_to_college_questionnaire_choices</t>
+          <t>student_adaptation_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1267,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>student_adaptation_to_college_questionnaire_choices</t>
+          <t>student_adaptation_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1322,40 +1276,6 @@
         </is>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>student_adaptation_to_college_questionnaire_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>student_adaptation_to_college_questionnaire_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
